--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -543,7 +543,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
     <t>配偶者、親、胎児、ドナーなど、このObservationのsubject要素が実際の対象でない場合、その実際の対象に関する情報</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1623,7 +1623,7 @@
     <t>【JP Core仕様】具体的な所見を記載する</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
